--- a/VerveStacks_NZL/vt_vervestacks_NZL_v1.xlsx
+++ b/VerveStacks_NZL/vt_vervestacks_NZL_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BB0F6310-0152-4F73-8E9B-2C12EC28E697}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B4A656CA-5E99-4AEA-87CB-D837BD566F50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{AEE85D5A-F491-4A57-98BB-6E7209DD8D75}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{98B2AD4B-C9E6-4CC0-B89E-42EDB66CA95C}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -1118,7 +1118,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35531FD9-4F74-4331-9A9B-9391964258AA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2CE70D2-E067-4BD1-898D-59DEFBF31129}">
   <dimension ref="B9:T36"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2648,7 +2648,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{971EA8F1-A691-41E8-A0C3-BB1DE8837947}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{302E34F4-1A2C-411C-8745-DA528894794F}">
   <dimension ref="B9:T113"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_NZL/vt_vervestacks_NZL_v1.xlsx
+++ b/VerveStacks_NZL/vt_vervestacks_NZL_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B4A656CA-5E99-4AEA-87CB-D837BD566F50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EFA02F7B-DFF9-45DB-B5DD-030646902862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{98B2AD4B-C9E6-4CC0-B89E-42EDB66CA95C}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{A46DD421-5B00-4D83-A1A5-9FA6B6E2181A}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -1118,7 +1118,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2CE70D2-E067-4BD1-898D-59DEFBF31129}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D33EC2C9-8567-40AE-8E13-16C4FCAE086C}">
   <dimension ref="B9:T36"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2648,7 +2648,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{302E34F4-1A2C-411C-8745-DA528894794F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97A68104-330A-4A20-99A2-A2F3AFE0C784}">
   <dimension ref="B9:T113"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_NZL/vt_vervestacks_NZL_v1.xlsx
+++ b/VerveStacks_NZL/vt_vervestacks_NZL_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EFA02F7B-DFF9-45DB-B5DD-030646902862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0DB9F433-9F21-4680-B74D-677463E9398C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{A46DD421-5B00-4D83-A1A5-9FA6B6E2181A}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{71F5A4CA-07EC-48ED-9CBD-65EE13318C70}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -354,7 +354,7 @@
     <t>ep_solar_pv_NZL</t>
   </si>
   <si>
-    <t>ep_windon_wind_c_won-NZL</t>
+    <t>ep_windon_wind_NZL</t>
   </si>
   <si>
     <t>windon</t>
@@ -1118,7 +1118,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D33EC2C9-8567-40AE-8E13-16C4FCAE086C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E61E618-4776-4839-890E-8F9056F95E97}">
   <dimension ref="B9:T36"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2648,7 +2648,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97A68104-330A-4A20-99A2-A2F3AFE0C784}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AFB6E64-DA70-4E91-9075-3502D1F5107E}">
   <dimension ref="B9:T113"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -7199,6 +7199,9 @@
       <c r="K95">
         <v>33</v>
       </c>
+      <c r="L95">
+        <v>0.19105738781268009</v>
+      </c>
       <c r="N95" t="s">
         <v>115</v>
       </c>
@@ -7252,8 +7255,11 @@
       <c r="K96">
         <v>40</v>
       </c>
-    </row>
-    <row r="97" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="L96">
+        <v>0.19281073694608941</v>
+      </c>
+    </row>
+    <row r="97" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B97" t="s">
         <v>104</v>
       </c>
@@ -7284,8 +7290,11 @@
       <c r="K97">
         <v>34</v>
       </c>
-    </row>
-    <row r="98" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="L97">
+        <v>0.19154116045114741</v>
+      </c>
+    </row>
+    <row r="98" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B98" t="s">
         <v>104</v>
       </c>
@@ -7316,8 +7325,11 @@
       <c r="K98">
         <v>32</v>
       </c>
-    </row>
-    <row r="99" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="L98">
+        <v>0.20177582940163952</v>
+      </c>
+    </row>
+    <row r="99" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B99" t="s">
         <v>104</v>
       </c>
@@ -7348,8 +7360,11 @@
       <c r="K99">
         <v>31</v>
       </c>
-    </row>
-    <row r="100" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="L99">
+        <v>0.1808007537346914</v>
+      </c>
+    </row>
+    <row r="100" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B100" t="s">
         <v>104</v>
       </c>
@@ -7380,8 +7395,11 @@
       <c r="K100">
         <v>30</v>
       </c>
-    </row>
-    <row r="101" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="L100">
+        <v>0.20117865406170704</v>
+      </c>
+    </row>
+    <row r="101" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B101" t="s">
         <v>104</v>
       </c>
@@ -7412,8 +7430,11 @@
       <c r="K101">
         <v>30</v>
       </c>
-    </row>
-    <row r="102" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="L101">
+        <v>0.18349581246367919</v>
+      </c>
+    </row>
+    <row r="102" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B102" t="s">
         <v>104</v>
       </c>
@@ -7444,8 +7465,11 @@
       <c r="K102">
         <v>30</v>
       </c>
-    </row>
-    <row r="103" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="L102">
+        <v>0.18579876762980663</v>
+      </c>
+    </row>
+    <row r="103" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B103" t="s">
         <v>105</v>
       </c>
@@ -7464,8 +7488,11 @@
       <c r="G103">
         <v>0.33123000000000002</v>
       </c>
-    </row>
-    <row r="104" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="L103">
+        <v>0.40395409929757359</v>
+      </c>
+    </row>
+    <row r="104" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B104" t="s">
         <v>105</v>
       </c>
@@ -7484,8 +7511,11 @@
       <c r="G104">
         <v>0.33123000000000002</v>
       </c>
-    </row>
-    <row r="105" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="L104">
+        <v>0.40395409929757359</v>
+      </c>
+    </row>
+    <row r="105" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B105" t="s">
         <v>105</v>
       </c>
@@ -7504,8 +7534,11 @@
       <c r="G105">
         <v>0.33123000000000002</v>
       </c>
-    </row>
-    <row r="106" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="L105">
+        <v>0.36401028944165292</v>
+      </c>
+    </row>
+    <row r="106" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B106" t="s">
         <v>105</v>
       </c>
@@ -7524,8 +7557,11 @@
       <c r="G106">
         <v>0.33123000000000002</v>
       </c>
-    </row>
-    <row r="107" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="L106">
+        <v>0.5383333233828641</v>
+      </c>
+    </row>
+    <row r="107" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B107" t="s">
         <v>105</v>
       </c>
@@ -7544,8 +7580,11 @@
       <c r="G107">
         <v>0.33123000000000008</v>
       </c>
-    </row>
-    <row r="108" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="L107">
+        <v>0.31775682128155458</v>
+      </c>
+    </row>
+    <row r="108" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B108" t="s">
         <v>105</v>
       </c>
@@ -7564,8 +7603,11 @@
       <c r="G108">
         <v>0.33123000000000002</v>
       </c>
-    </row>
-    <row r="109" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="L108">
+        <v>0.5665247689951628</v>
+      </c>
+    </row>
+    <row r="109" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B109" t="s">
         <v>105</v>
       </c>
@@ -7584,8 +7626,11 @@
       <c r="G109">
         <v>0.33123000000000002</v>
       </c>
-    </row>
-    <row r="110" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="L109">
+        <v>0.4739763845441875</v>
+      </c>
+    </row>
+    <row r="110" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B110" t="s">
         <v>105</v>
       </c>
@@ -7604,8 +7649,11 @@
       <c r="G110">
         <v>0.33123000000000002</v>
       </c>
-    </row>
-    <row r="111" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="L110">
+        <v>0.42171477135214525</v>
+      </c>
+    </row>
+    <row r="111" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B111" t="s">
         <v>105</v>
       </c>
@@ -7624,8 +7672,11 @@
       <c r="G111">
         <v>0.33123000000000008</v>
       </c>
-    </row>
-    <row r="112" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="L111">
+        <v>0.42855807852917049</v>
+      </c>
+    </row>
+    <row r="112" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B112" t="s">
         <v>105</v>
       </c>
@@ -7644,8 +7695,11 @@
       <c r="G112">
         <v>0.33123000000000002</v>
       </c>
-    </row>
-    <row r="113" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="L112">
+        <v>0.28243194746500749</v>
+      </c>
+    </row>
+    <row r="113" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B113" t="s">
         <v>105</v>
       </c>
@@ -7663,6 +7717,9 @@
       </c>
       <c r="G113">
         <v>0.33123000000000002</v>
+      </c>
+      <c r="L113">
+        <v>0.43764790128670528</v>
       </c>
     </row>
   </sheetData>
